--- a/public/Plantilla_Migracion_Casos_Prueba_tmp.xlsx
+++ b/public/Plantilla_Migracion_Casos_Prueba_tmp.xlsx
@@ -1,29 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\webApps\parque_espana\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE8ECAE-445D-4E50-A25F-77140D99DFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="7" autoFilterDateGrouping="true" firstSheet="1" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" r:id="rId4"/>
-    <sheet name="1. Usuarios" sheetId="2" r:id="rId5"/>
-    <sheet name="2. Membresias" sheetId="3" r:id="rId6"/>
-    <sheet name="3. Integrantes" sheetId="4" r:id="rId7"/>
-    <sheet name="4. Domicilios" sheetId="5" r:id="rId8"/>
-    <sheet name="5. Empleo" sheetId="6" r:id="rId9"/>
-    <sheet name="6. Catálogos" sheetId="7" r:id="rId10"/>
-    <sheet name="8. Historial por Período" sheetId="8" r:id="rId11"/>
-    <sheet name="9. Casilleros" sheetId="9" r:id="rId12"/>
+    <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
+    <sheet name="1. Usuarios" sheetId="2" r:id="rId2"/>
+    <sheet name="2. Membresias" sheetId="3" r:id="rId3"/>
+    <sheet name="3. Integrantes" sheetId="4" r:id="rId4"/>
+    <sheet name="4. Domicilios" sheetId="5" r:id="rId5"/>
+    <sheet name="5. Empleo" sheetId="6" r:id="rId6"/>
+    <sheet name="6. Catálogos" sheetId="7" r:id="rId7"/>
+    <sheet name="8. Historial por Período" sheetId="8" r:id="rId8"/>
+    <sheet name="9. Casilleros" sheetId="9" r:id="rId9"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="501">
   <si>
     <t>PLANTILLA DE MIGRACIÓN DE DATOS</t>
   </si>
@@ -1508,185 +1513,162 @@
   </si>
   <si>
     <t>⚠  Incluir solo asignaciones vigentes o con historial relevante. Si el casillero tiene cobro asociado, registrar el pago en la hoja "8. Historial por Período" con concepto LOCKERS.</t>
+  </si>
+  <si>
+    <t>TEST-U23</t>
+  </si>
+  <si>
+    <t>Paula</t>
+  </si>
+  <si>
+    <t>Sosa</t>
+  </si>
+  <si>
+    <t>Barragan</t>
+  </si>
+  <si>
+    <t>paula.sosa@test.com</t>
+  </si>
+  <si>
+    <t>TEST-015</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFC0392B"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF2980B9"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1E8449"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="1"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF7D6608"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="1"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <i/>
       <sz val="8"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="1"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="8"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="22">
@@ -1919,182 +1901,169 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+  <cellXfs count="59">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="8" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="9" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="10" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="11" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="12" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="13" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="10" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="10" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="11" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="12" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="12" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="12" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="13" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="13" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="13" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="14" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="15" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="16" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="16" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="17" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="18" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="8" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="18" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="14" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="16" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="19" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="11" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="14" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="12" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="15" numFmtId="0" fillId="11" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="19" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="20" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="21" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="16" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="17" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="18" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="11" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="12" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="14" fillId="12" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="15" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2324,38 +2293,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="true" style="1"/>
-    <col min="2" max="2" width="28" customWidth="true" style="1"/>
-    <col min="3" max="3" width="60" customWidth="true" style="1"/>
+    <col min="1" max="1" width="3" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28" style="1" customWidth="1"/>
+    <col min="3" max="3" width="60" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="1" ht="31.5">
-      <c r="B1" s="37" t="s">
+    <row r="1" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="34"/>
-    </row>
-    <row r="2" spans="1:6" customHeight="1" ht="18">
-      <c r="B2" s="36" t="s">
+      <c r="C1" s="47"/>
+    </row>
+    <row r="2" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="34"/>
-    </row>
-    <row r="3" spans="1:6" customHeight="1" ht="7.5"/>
-    <row r="4" spans="1:6" customHeight="1" ht="18">
-      <c r="B4" s="35" t="s">
+      <c r="C2" s="47"/>
+    </row>
+    <row r="3" spans="2:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="34"/>
-    </row>
-    <row r="5" spans="1:6" customHeight="1" ht="15.75">
+      <c r="C4" s="47"/>
+    </row>
+    <row r="5" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2363,7 +2329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" customHeight="1" ht="18">
+    <row r="6" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2371,7 +2337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" customHeight="1" ht="18">
+    <row r="7" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
@@ -2379,7 +2345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" customHeight="1" ht="27.75">
+    <row r="8" spans="2:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
@@ -2387,7 +2353,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" customHeight="1" ht="18">
+    <row r="9" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -2395,7 +2361,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" customHeight="1" ht="18">
+    <row r="10" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
@@ -2403,7 +2369,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" customHeight="1" ht="18">
+    <row r="11" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
@@ -2411,14 +2377,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" customHeight="1" ht="7.5"/>
-    <row r="13" spans="1:6" customHeight="1" ht="18">
-      <c r="B13" s="35" t="s">
+    <row r="12" spans="2:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="34"/>
-    </row>
-    <row r="14" spans="1:6" customHeight="1" ht="18">
+      <c r="C13" s="47"/>
+    </row>
+    <row r="14" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
@@ -2426,7 +2392,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:6" customHeight="1" ht="27.75">
+    <row r="15" spans="2:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
@@ -2434,7 +2400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:6" customHeight="1" ht="18">
+    <row r="16" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
@@ -2442,7 +2408,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:6" customHeight="1" ht="18">
+    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
@@ -2450,7 +2416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:6" customHeight="1" ht="27.75">
+    <row r="18" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>26</v>
       </c>
@@ -2458,14 +2424,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:6" customHeight="1" ht="7.5"/>
-    <row r="20" spans="1:6" customHeight="1" ht="18">
-      <c r="B20" s="35" t="s">
+    <row r="19" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="34"/>
-    </row>
-    <row r="21" spans="1:6" customHeight="1" ht="15.75">
+      <c r="C20" s="47"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
@@ -2473,7 +2439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:6" customHeight="1" ht="15.75">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
         <v>31</v>
       </c>
@@ -2481,7 +2447,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:6" customHeight="1" ht="15.75">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
         <v>33</v>
       </c>
@@ -2489,18 +2455,18 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:6" customHeight="1" ht="21.9">
-      <c r="A25" s="33" t="s">
+    <row r="25" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="6">
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B2:C2"/>
@@ -2508,64 +2474,45 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AB26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="true" style="1"/>
-    <col min="2" max="2" width="22" customWidth="true" style="1"/>
-    <col min="3" max="3" width="22" customWidth="true" style="1"/>
-    <col min="4" max="4" width="22" customWidth="true" style="1"/>
-    <col min="5" max="5" width="18" customWidth="true" style="1"/>
-    <col min="6" max="6" width="16" customWidth="true" style="1"/>
-    <col min="7" max="7" width="28" customWidth="true" style="1"/>
-    <col min="8" max="8" width="20" customWidth="true" style="1"/>
-    <col min="9" max="9" width="20" customWidth="true" style="1"/>
-    <col min="10" max="10" width="20" customWidth="true" style="1"/>
-    <col min="11" max="11" width="18" customWidth="true" style="1"/>
-    <col min="12" max="12" width="18" customWidth="true" style="1"/>
-    <col min="13" max="13" width="24" customWidth="true" style="1"/>
-    <col min="14" max="14" width="24" customWidth="true" style="1"/>
-    <col min="15" max="15" width="8.21875" customWidth="true" style="0"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="4" width="22" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28" style="1" customWidth="1"/>
+    <col min="8" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="12" width="18" style="1" customWidth="1"/>
+    <col min="13" max="14" width="24" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" customHeight="1" ht="25.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -2580,7 +2527,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" customHeight="1" ht="31.5">
+    <row r="2" spans="1:28" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>20</v>
       </c>
@@ -2626,57 +2573,55 @@
       <c r="O2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AB2"/>
-    </row>
-    <row r="3" spans="1:28" customHeight="1" ht="42">
-      <c r="A3" s="43" t="s">
+    </row>
+    <row r="3" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="J3" s="43" t="s">
+      <c r="J3" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="43" t="s">
+      <c r="K3" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="L3" s="43" t="s">
+      <c r="L3" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="M3" s="43" t="s">
+      <c r="M3" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="N3" s="43" t="s">
+      <c r="N3" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="AB3"/>
-    </row>
-    <row r="4" spans="1:28">
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>66</v>
       </c>
@@ -2716,12 +2661,11 @@
       <c r="M4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="1"/>
       <c r="O4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>79</v>
       </c>
@@ -2761,12 +2705,11 @@
       <c r="M5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="N5" s="1"/>
       <c r="O5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>86</v>
       </c>
@@ -2806,12 +2749,11 @@
       <c r="M6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="N6" s="1"/>
       <c r="O6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>94</v>
       </c>
@@ -2851,12 +2793,11 @@
       <c r="M7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="1"/>
       <c r="O7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -2896,12 +2837,11 @@
       <c r="M8" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N8" s="1"/>
       <c r="O8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>105</v>
       </c>
@@ -2941,12 +2881,11 @@
       <c r="M9" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="N9" s="1"/>
       <c r="O9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>113</v>
       </c>
@@ -2986,12 +2925,11 @@
       <c r="M10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="N10" s="1"/>
       <c r="O10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>117</v>
       </c>
@@ -3031,12 +2969,11 @@
       <c r="M11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N11" s="1"/>
       <c r="O11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>123</v>
       </c>
@@ -3076,12 +3013,11 @@
       <c r="M12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="1"/>
       <c r="O12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>127</v>
       </c>
@@ -3121,12 +3057,11 @@
       <c r="M13" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="N13" s="1"/>
       <c r="O13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>133</v>
       </c>
@@ -3166,12 +3101,11 @@
       <c r="M14" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="N14" s="1"/>
       <c r="O14" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>136</v>
       </c>
@@ -3211,12 +3145,11 @@
       <c r="M15" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="N15" s="1"/>
       <c r="O15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>142</v>
       </c>
@@ -3256,12 +3189,11 @@
       <c r="M16" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="N16" s="1"/>
       <c r="O16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>145</v>
       </c>
@@ -3301,12 +3233,11 @@
       <c r="M17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="N17" s="1"/>
       <c r="O17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>150</v>
       </c>
@@ -3346,12 +3277,11 @@
       <c r="M18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N18" s="1"/>
       <c r="O18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>154</v>
       </c>
@@ -3391,12 +3321,11 @@
       <c r="M19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N19" s="1"/>
       <c r="O19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>158</v>
       </c>
@@ -3436,12 +3365,11 @@
       <c r="M20" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="N20" s="1"/>
       <c r="O20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>162</v>
       </c>
@@ -3481,12 +3409,11 @@
       <c r="M21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="N21" s="1"/>
       <c r="O21" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>165</v>
       </c>
@@ -3526,12 +3453,11 @@
       <c r="M22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="N22" s="1"/>
       <c r="O22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>168</v>
       </c>
@@ -3571,12 +3497,11 @@
       <c r="M23" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="N23" s="1"/>
       <c r="O23" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -3616,12 +3541,11 @@
       <c r="M24" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="N24" s="1"/>
       <c r="O24" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>178</v>
       </c>
@@ -3661,71 +3585,105 @@
       <c r="M25" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="N25" s="1"/>
       <c r="O25" t="s">
         <v>78</v>
       </c>
     </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="E26" s="55">
+        <v>26478</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5510000022</v>
+      </c>
+      <c r="G26" s="57" t="s">
+        <v>499</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O26" s="56" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G26" r:id="rId1" xr:uid="{F73CC8AE-2874-4DE8-929F-BE61CCBCEC52}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="true" style="1"/>
-    <col min="2" max="2" width="26" customWidth="true" style="1"/>
-    <col min="3" max="3" width="18" customWidth="true" style="1"/>
-    <col min="4" max="4" width="22" customWidth="true" style="1"/>
-    <col min="5" max="5" width="16" customWidth="true" style="1"/>
-    <col min="6" max="6" width="14" customWidth="true" style="0"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" customHeight="1" ht="25.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-    </row>
-    <row r="2" spans="1:7" customHeight="1" ht="31.5">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>184</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>186</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>188</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -3735,30 +3693,30 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:7" customHeight="1" ht="42">
-      <c r="A3" s="43" t="s">
+    <row r="3" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="24" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>196</v>
       </c>
@@ -3768,8 +3726,6 @@
       <c r="C4" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
       <c r="F4" t="s">
         <v>199</v>
       </c>
@@ -3777,7 +3733,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>201</v>
       </c>
@@ -3787,8 +3743,6 @@
       <c r="C5" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
       <c r="F5" t="s">
         <v>202</v>
       </c>
@@ -3796,7 +3750,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>203</v>
       </c>
@@ -3806,8 +3760,6 @@
       <c r="C6" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
       <c r="F6" t="s">
         <v>205</v>
       </c>
@@ -3815,7 +3767,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>206</v>
       </c>
@@ -3825,8 +3777,6 @@
       <c r="C7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
       <c r="F7" t="s">
         <v>209</v>
       </c>
@@ -3834,7 +3784,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>210</v>
       </c>
@@ -3844,8 +3794,6 @@
       <c r="C8" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
       <c r="F8" t="s">
         <v>212</v>
       </c>
@@ -3853,7 +3801,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>213</v>
       </c>
@@ -3863,8 +3811,6 @@
       <c r="C9" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
       <c r="F9" t="s">
         <v>215</v>
       </c>
@@ -3872,7 +3818,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>216</v>
       </c>
@@ -3882,8 +3828,6 @@
       <c r="C10" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
       <c r="F10" t="s">
         <v>217</v>
       </c>
@@ -3891,7 +3835,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>218</v>
       </c>
@@ -3901,8 +3845,6 @@
       <c r="C11" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
       <c r="F11" t="s">
         <v>220</v>
       </c>
@@ -3910,7 +3852,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>221</v>
       </c>
@@ -3923,7 +3865,6 @@
       <c r="D12" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E12" s="1"/>
       <c r="F12" t="s">
         <v>224</v>
       </c>
@@ -3931,7 +3872,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>225</v>
       </c>
@@ -3944,7 +3885,6 @@
       <c r="D13" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E13" s="1"/>
       <c r="F13" t="s">
         <v>226</v>
       </c>
@@ -3952,7 +3892,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>227</v>
       </c>
@@ -3965,7 +3905,6 @@
       <c r="D14" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="1"/>
       <c r="F14" t="s">
         <v>229</v>
       </c>
@@ -3973,7 +3912,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>230</v>
       </c>
@@ -3986,7 +3925,6 @@
       <c r="D15" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E15" s="1"/>
       <c r="F15" t="s">
         <v>232</v>
       </c>
@@ -3994,7 +3932,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>233</v>
       </c>
@@ -4007,7 +3945,6 @@
       <c r="D16" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E16" s="1"/>
       <c r="F16" t="s">
         <v>236</v>
       </c>
@@ -4015,7 +3952,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>237</v>
       </c>
@@ -4028,7 +3965,6 @@
       <c r="D17" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E17" s="1"/>
       <c r="F17" t="s">
         <v>238</v>
       </c>
@@ -4036,48 +3972,51 @@
         <v>200</v>
       </c>
     </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="56" t="s">
+        <v>500</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="F18" s="58">
+        <v>44348</v>
+      </c>
+      <c r="G18" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="true" style="1"/>
-    <col min="2" max="2" width="16" customWidth="true" style="1"/>
-    <col min="3" max="3" width="12" customWidth="true" style="1"/>
-    <col min="4" max="4" width="20" customWidth="true" style="1"/>
+    <col min="1" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" customHeight="1" ht="25.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-    </row>
-    <row r="2" spans="1:4" customHeight="1" ht="31.5">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+    </row>
+    <row r="2" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>184</v>
       </c>
@@ -4091,21 +4030,21 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:4" customHeight="1" ht="42">
-      <c r="A3" s="43" t="s">
+    <row r="3" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="24" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>196</v>
       </c>
@@ -4115,9 +4054,8 @@
       <c r="C4" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>196</v>
       </c>
@@ -4131,7 +4069,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>201</v>
       </c>
@@ -4141,9 +4079,8 @@
       <c r="C6" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>201</v>
       </c>
@@ -4157,7 +4094,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>203</v>
       </c>
@@ -4167,9 +4104,8 @@
       <c r="C8" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>206</v>
       </c>
@@ -4179,9 +4115,8 @@
       <c r="C9" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>206</v>
       </c>
@@ -4195,7 +4130,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>210</v>
       </c>
@@ -4205,9 +4140,8 @@
       <c r="C11" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>210</v>
       </c>
@@ -4221,7 +4155,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>213</v>
       </c>
@@ -4231,9 +4165,8 @@
       <c r="C13" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>213</v>
       </c>
@@ -4247,7 +4180,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>216</v>
       </c>
@@ -4257,9 +4190,8 @@
       <c r="C15" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>216</v>
       </c>
@@ -4273,7 +4205,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>218</v>
       </c>
@@ -4283,9 +4215,8 @@
       <c r="C17" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>221</v>
       </c>
@@ -4295,9 +4226,8 @@
       <c r="C18" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>225</v>
       </c>
@@ -4307,9 +4237,8 @@
       <c r="C19" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>227</v>
       </c>
@@ -4319,9 +4248,8 @@
       <c r="C20" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>227</v>
       </c>
@@ -4335,7 +4263,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>227</v>
       </c>
@@ -4349,7 +4277,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>227</v>
       </c>
@@ -4363,7 +4291,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>230</v>
       </c>
@@ -4373,9 +4301,8 @@
       <c r="C24" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:4">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>230</v>
       </c>
@@ -4389,7 +4316,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>230</v>
       </c>
@@ -4403,7 +4330,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>230</v>
       </c>
@@ -4417,7 +4344,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>233</v>
       </c>
@@ -4427,9 +4354,8 @@
       <c r="C28" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>233</v>
       </c>
@@ -4443,7 +4369,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>233</v>
       </c>
@@ -4457,7 +4383,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>237</v>
       </c>
@@ -4467,9 +4393,8 @@
       <c r="C31" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:4">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>237</v>
       </c>
@@ -4483,7 +4408,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>237</v>
       </c>
@@ -4497,56 +4422,53 @@
         <v>248</v>
       </c>
     </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="56" t="s">
+        <v>500</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="true" style="1"/>
-    <col min="2" max="2" width="30" customWidth="true" style="1"/>
-    <col min="3" max="3" width="24" customWidth="true" style="1"/>
-    <col min="4" max="4" width="14" customWidth="true" style="1"/>
-    <col min="5" max="5" width="18" customWidth="true" style="1"/>
-    <col min="6" max="6" width="20" customWidth="true" style="1"/>
-    <col min="7" max="7" width="20" customWidth="true" style="1"/>
-    <col min="8" max="8" width="16" customWidth="true" style="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="1" customWidth="1"/>
+    <col min="6" max="7" width="20" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customHeight="1" ht="25.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="2" spans="1:8" customHeight="1" ht="31.5">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+    </row>
+    <row r="2" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>20</v>
       </c>
@@ -4572,217 +4494,204 @@
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:8" customHeight="1" ht="42">
-      <c r="A3" s="43" t="s">
+    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="24" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="24" t="s">
         <v>260</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="24" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:8" customHeight="1" ht="15">
-      <c r="A4" s="44" t="s">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="44">
+      <c r="H4" s="25">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" customHeight="1" ht="15">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="25">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" customHeight="1" ht="15">
-      <c r="A6" s="44" t="s">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="25" t="s">
         <v>274</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="25">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" customHeight="1" ht="15">
-      <c r="A7" s="44" t="s">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F7" s="44" t="s">
+      <c r="F7" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="44" t="s">
+      <c r="G7" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="25">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" customHeight="1" ht="15">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="25">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" customHeight="1" ht="15">
-      <c r="A10" s="38" t="s">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="true" style="1"/>
-    <col min="2" max="2" width="28" customWidth="true" style="1"/>
-    <col min="3" max="3" width="36" customWidth="true" style="1"/>
-    <col min="4" max="4" width="18" customWidth="true" style="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" customHeight="1" ht="25.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-    </row>
-    <row r="2" spans="1:4" customHeight="1" ht="31.5">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+    </row>
+    <row r="2" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>20</v>
       </c>
@@ -4796,2119 +4705,2063 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:4" customHeight="1" ht="42">
-      <c r="A3" s="43" t="s">
+    <row r="3" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="24" t="s">
         <v>286</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="24" t="s">
         <v>287</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="24" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="4" spans="1:4" customHeight="1" ht="23.85">
-      <c r="A4" s="44" t="s">
+    <row r="4" spans="1:4" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="25" t="s">
         <v>290</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="25" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:4" customHeight="1" ht="15">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="25" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="6" spans="1:4" customHeight="1" ht="15">
-      <c r="A6" s="44" t="s">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="25" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="8" spans="1:4" customHeight="1" ht="15">
-      <c r="A8" s="38" t="s">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="52" t="s">
         <v>298</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="true" style="1"/>
-    <col min="3" max="3" width="28" customWidth="true" style="1"/>
-    <col min="5" max="5" width="28" customWidth="true" style="1"/>
-    <col min="7" max="7" width="44" customWidth="true" style="1"/>
-    <col min="8" max="8" width="44" customWidth="true" style="1"/>
-    <col min="11" max="11" width="22" customWidth="true" style="1"/>
-    <col min="12" max="12" width="30" customWidth="true" style="1"/>
-    <col min="13" max="13" width="20" customWidth="true" style="1"/>
-    <col min="16" max="16" width="20" customWidth="true" style="1"/>
-    <col min="17" max="17" width="33.109375" customWidth="true" style="1"/>
+    <col min="1" max="1" width="28" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28" style="1" customWidth="1"/>
+    <col min="7" max="8" width="44" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="1" customWidth="1"/>
+    <col min="12" max="12" width="30" style="1" customWidth="1"/>
+    <col min="13" max="13" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="33.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" customHeight="1" ht="25.5">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="31"/>
-      <c r="K1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="44"/>
+      <c r="K1" s="53" t="s">
         <v>300</v>
       </c>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="P1" s="40" t="s">
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="P1" s="53" t="s">
         <v>301</v>
       </c>
-      <c r="Q1" s="34"/>
-    </row>
-    <row r="2" spans="1:17" customHeight="1" ht="27.75">
-      <c r="A2" s="46" t="s">
+      <c r="Q1" s="47"/>
+    </row>
+    <row r="2" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="27" t="s">
         <v>302</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="H2" s="46" t="s">
+      <c r="H2" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="46" t="s">
+      <c r="I2" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="K2" s="53" t="s">
+      <c r="K2" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="L2" s="53" t="s">
+      <c r="L2" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="54" t="s">
+      <c r="M2" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="P2" s="53" t="s">
+      <c r="P2" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="Q2" s="53" t="s">
+      <c r="Q2" s="34" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:17" customHeight="1" ht="23.85">
-      <c r="A3" s="52" t="s">
+    <row r="3" spans="1:17" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="31" t="s">
         <v>307</v>
       </c>
-      <c r="I3" s="49" t="s">
+      <c r="I3" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="K3" s="56" t="s">
+      <c r="K3" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="36" t="s">
         <v>309</v>
       </c>
-      <c r="M3" s="55" t="s">
+      <c r="M3" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="Q3" s="55" t="s">
+      <c r="Q3" s="36" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="4" spans="1:17" customHeight="1" ht="15">
-      <c r="A4" s="52" t="s">
+    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="I4" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="K4" s="56" t="s">
+      <c r="K4" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="36" t="s">
         <v>315</v>
       </c>
-      <c r="M4" s="55" t="s">
+      <c r="M4" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="P4" s="56" t="s">
+      <c r="P4" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="Q4" s="55" t="s">
+      <c r="Q4" s="36" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:17" customHeight="1" ht="15">
-      <c r="A5" s="52" t="s">
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H5" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="I5" s="49" t="s">
+      <c r="I5" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="K5" s="56" t="s">
+      <c r="K5" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="L5" s="55" t="s">
+      <c r="L5" s="36" t="s">
         <v>323</v>
       </c>
-      <c r="M5" s="55" t="s">
+      <c r="M5" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="P5" s="56" t="s">
+      <c r="P5" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="Q5" s="55" t="s">
+      <c r="Q5" s="36" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:17" customHeight="1" ht="15">
-      <c r="A6" s="52" t="s">
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
         <v>325</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="H6" s="50" t="s">
+      <c r="H6" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="I6" s="49" t="s">
+      <c r="I6" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="K6" s="56" t="s">
+      <c r="K6" s="37" t="s">
         <v>330</v>
       </c>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="36" t="s">
         <v>331</v>
       </c>
-      <c r="M6" s="55" t="s">
+      <c r="M6" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="P6" s="56" t="s">
+      <c r="P6" s="37" t="s">
         <v>332</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="38" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="7" spans="1:17" customHeight="1" ht="15">
-      <c r="A7" s="52" t="s">
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="33" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="33" t="s">
         <v>335</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="31" t="s">
         <v>337</v>
       </c>
-      <c r="I7" s="49" t="s">
+      <c r="I7" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="K7" s="56" t="s">
+      <c r="K7" s="37" t="s">
         <v>338</v>
       </c>
-      <c r="L7" s="55" t="s">
+      <c r="L7" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="M7" s="55" t="s">
+      <c r="M7" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="P7" s="58" t="s">
+      <c r="P7" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="Q7" s="57" t="s">
+      <c r="Q7" s="38" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
-      <c r="G8" s="48" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G8" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="I8" s="49" t="s">
+      <c r="I8" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="K8" s="56" t="s">
+      <c r="K8" s="37" t="s">
         <v>343</v>
       </c>
-      <c r="L8" s="55" t="s">
+      <c r="L8" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="M8" s="55" t="s">
+      <c r="M8" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="P8" s="56" t="s">
+      <c r="P8" s="37" t="s">
         <v>345</v>
       </c>
-      <c r="Q8" s="55" t="s">
+      <c r="Q8" s="36" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="9" spans="1:17" customHeight="1" ht="15">
+    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="H9" s="50" t="s">
+      <c r="H9" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="I9" s="49" t="s">
+      <c r="I9" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="P9" s="56" t="s">
+      <c r="P9" s="37" t="s">
         <v>350</v>
       </c>
-      <c r="Q9" s="55" t="s">
+      <c r="Q9" s="36" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
-      <c r="G10" s="48" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G10" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="H10" s="50" t="s">
+      <c r="H10" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="I10" s="49" t="s">
+      <c r="I10" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="P10" s="56" t="s">
+      <c r="P10" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="Q10" s="55" t="s">
+      <c r="Q10" s="36" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
-      <c r="G11" s="48" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G11" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="31" t="s">
         <v>356</v>
       </c>
-      <c r="I11" s="49" t="s">
+      <c r="I11" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="P11" s="56" t="s">
+      <c r="P11" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="Q11" s="55" t="s">
+      <c r="Q11" s="36" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
-      <c r="G12" s="48" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G12" s="29" t="s">
         <v>359</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="31" t="s">
         <v>360</v>
       </c>
-      <c r="I12" s="49" t="s">
+      <c r="I12" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="P12" s="56" t="s">
+      <c r="P12" s="37" t="s">
         <v>361</v>
       </c>
-      <c r="Q12" s="55" t="s">
+      <c r="Q12" s="36" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
-      <c r="G13" s="48" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G13" s="29" t="s">
         <v>363</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="I13" s="49" t="s">
+      <c r="I13" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="G14" s="48" t="s">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G14" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="H14" s="50" t="s">
+      <c r="H14" s="31" t="s">
         <v>365</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
-      <c r="G15" s="48" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G15" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="H15" s="50" t="s">
+      <c r="H15" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="I15" s="49" t="s">
+      <c r="I15" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
-      <c r="G16" s="48" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G16" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="H16" s="50" t="s">
+      <c r="H16" s="31" t="s">
         <v>337</v>
       </c>
-      <c r="I16" s="49" t="s">
+      <c r="I16" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
-      <c r="G17" s="48" t="s">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G17" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="I17" s="49" t="s">
+      <c r="I17" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
-      <c r="G18" s="48" t="s">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G18" s="29" t="s">
         <v>369</v>
       </c>
-      <c r="H18" s="50" t="s">
+      <c r="H18" s="31" t="s">
         <v>370</v>
       </c>
-      <c r="I18" s="49" t="s">
+      <c r="I18" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
-      <c r="G19" s="48" t="s">
+    <row r="19" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G19" s="29" t="s">
         <v>371</v>
       </c>
-      <c r="H19" s="50" t="s">
+      <c r="H19" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="I19" s="49" t="s">
+      <c r="I19" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
-      <c r="G20" s="48" t="s">
+    <row r="20" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G20" s="29" t="s">
         <v>373</v>
       </c>
-      <c r="H20" s="50" t="s">
+      <c r="H20" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
-      <c r="G21" s="48" t="s">
+    <row r="21" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="29" t="s">
         <v>375</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="31" t="s">
         <v>376</v>
       </c>
-      <c r="I21" s="49" t="s">
+      <c r="I21" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
-      <c r="G22" s="48" t="s">
+    <row r="22" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G22" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="31" t="s">
         <v>377</v>
       </c>
-      <c r="I22" s="49" t="s">
+      <c r="I22" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
-      <c r="G23" s="51" t="s">
+    <row r="23" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G23" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="H23" s="47" t="s">
+      <c r="H23" s="28" t="s">
         <v>378</v>
       </c>
-      <c r="I23" s="49" t="s">
+      <c r="I23" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
-      <c r="G24" s="51" t="s">
+    <row r="24" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G24" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="H24" s="47" t="s">
+      <c r="H24" s="28" t="s">
         <v>380</v>
       </c>
-      <c r="I24" s="49" t="s">
+      <c r="I24" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
-      <c r="G25" s="51" t="s">
+    <row r="25" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G25" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="H25" s="47" t="s">
+      <c r="H25" s="28" t="s">
         <v>381</v>
       </c>
-      <c r="I25" s="49" t="s">
+      <c r="I25" s="30" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
+    <row r="26" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.88671875" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10" customWidth="true" style="0"/>
-    <col min="3" max="3" width="22" customWidth="true" style="0"/>
-    <col min="4" max="4" width="30" customWidth="true" style="0"/>
-    <col min="5" max="5" width="8" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.77734375" customWidth="true" style="0"/>
-    <col min="7" max="7" width="19.5546875" customWidth="true" style="0"/>
-    <col min="8" max="8" width="18" customWidth="true" style="0"/>
-    <col min="9" max="9" width="14" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16" customWidth="true" style="0"/>
-    <col min="11" max="11" width="23.88671875" customWidth="true" style="0"/>
-    <col min="12" max="12" width="16" customWidth="true" style="0"/>
-    <col min="13" max="13" width="18" customWidth="true" style="0"/>
-    <col min="14" max="14" width="16" customWidth="true" style="0"/>
-    <col min="15" max="15" width="14" customWidth="true" style="0"/>
-    <col min="16" max="16" width="30" customWidth="true" style="0"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="23.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" customHeight="1" ht="25.5">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>382</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-    </row>
-    <row r="2" spans="1:16" customHeight="1" ht="31.5">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+    </row>
+    <row r="2" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="15" t="s">
         <v>392</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="15" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:16" customHeight="1" ht="42">
-      <c r="A3" s="59" t="s">
+    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="40" t="s">
         <v>396</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="40" t="s">
         <v>397</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="40" t="s">
         <v>398</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="40" t="s">
         <v>399</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="40" t="s">
         <v>400</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="40" t="s">
         <v>401</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="40" t="s">
         <v>402</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="40" t="s">
         <v>403</v>
       </c>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="40" t="s">
         <v>404</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="40" t="s">
         <v>405</v>
       </c>
-      <c r="K3" s="59" t="s">
+      <c r="K3" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="L3" s="59" t="s">
+      <c r="L3" s="40" t="s">
         <v>407</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="40" t="s">
         <v>408</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="40" t="s">
         <v>408</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="40" t="s">
         <v>409</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="40" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="4" spans="1:16" customHeight="1" ht="15">
-      <c r="A4" s="61" t="s">
+    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="31">
         <v>2019</v>
       </c>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61">
+      <c r="F4" s="31"/>
+      <c r="G4" s="31">
         <v>85000</v>
       </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61">
+      <c r="H4" s="31"/>
+      <c r="I4" s="31">
         <v>85000</v>
       </c>
-      <c r="J4" s="61" t="s">
+      <c r="J4" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="K4" s="61" t="s">
+      <c r="K4" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61" t="s">
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31" t="s">
         <v>414</v>
       </c>
-      <c r="P4" s="61"/>
-    </row>
-    <row r="5" spans="1:16" customHeight="1" ht="15">
-      <c r="A5" s="61" t="s">
+      <c r="P4" s="31"/>
+    </row>
+    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="31" t="s">
         <v>415</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="31">
         <v>2019</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="31">
         <v>3</v>
       </c>
-      <c r="G5" s="61">
+      <c r="G5" s="31">
         <v>3000</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61">
+      <c r="H5" s="31"/>
+      <c r="I5" s="31">
         <v>3000</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="J5" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="K5" s="61" t="s">
+      <c r="K5" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61" t="s">
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31" t="s">
         <v>414</v>
       </c>
-      <c r="P5" s="61"/>
-    </row>
-    <row r="6" spans="1:16" customHeight="1" ht="15">
-      <c r="A6" s="61" t="s">
+      <c r="P5" s="31"/>
+    </row>
+    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="31" t="s">
         <v>416</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="31">
         <v>2019</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="31">
         <v>4</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G6" s="31">
         <v>3000</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61">
+      <c r="H6" s="31"/>
+      <c r="I6" s="31">
         <v>3000</v>
       </c>
-      <c r="J6" s="61" t="s">
+      <c r="J6" s="31" t="s">
         <v>417</v>
       </c>
-      <c r="K6" s="61" t="s">
+      <c r="K6" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-    </row>
-    <row r="7" spans="1:16" customHeight="1" ht="15">
-      <c r="A7" s="61" t="s">
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+    </row>
+    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D7" s="61" t="s">
+      <c r="D7" s="31" t="s">
         <v>418</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="31">
         <v>2019</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="31">
         <v>5</v>
       </c>
-      <c r="G7" s="61">
+      <c r="G7" s="31">
         <v>3000</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61">
+      <c r="H7" s="31"/>
+      <c r="I7" s="31">
         <v>3000</v>
       </c>
-      <c r="J7" s="61" t="s">
+      <c r="J7" s="31" t="s">
         <v>419</v>
       </c>
-      <c r="K7" s="61" t="s">
+      <c r="K7" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="L7" s="61" t="s">
+      <c r="L7" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="61" t="s">
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31" t="s">
         <v>421</v>
       </c>
-      <c r="P7" s="61"/>
-    </row>
-    <row r="8" spans="1:16" customHeight="1" ht="15">
-      <c r="A8" s="61" t="s">
+      <c r="P7" s="31"/>
+    </row>
+    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="31" t="s">
         <v>422</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="31">
         <v>2019</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="31">
         <v>6</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="31">
         <v>3000</v>
       </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61">
+      <c r="H8" s="31"/>
+      <c r="I8" s="31">
         <v>3000</v>
       </c>
-      <c r="J8" s="61" t="s">
+      <c r="J8" s="31" t="s">
         <v>419</v>
       </c>
-      <c r="K8" s="61" t="s">
+      <c r="K8" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="L8" s="61" t="s">
+      <c r="L8" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="M8" s="61"/>
-      <c r="N8" s="61"/>
-      <c r="O8" s="61" t="s">
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31" t="s">
         <v>421</v>
       </c>
-      <c r="P8" s="61"/>
-    </row>
-    <row r="9" spans="1:16" customHeight="1" ht="15">
-      <c r="A9" s="61" t="s">
+      <c r="P8" s="31"/>
+    </row>
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="31" t="s">
         <v>423</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="31">
         <v>2019</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="31">
         <v>7</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="31">
         <v>3000</v>
       </c>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61">
+      <c r="H9" s="31"/>
+      <c r="I9" s="31">
         <v>3000</v>
       </c>
-      <c r="J9" s="61" t="s">
+      <c r="J9" s="31" t="s">
         <v>419</v>
       </c>
-      <c r="K9" s="61" t="s">
+      <c r="K9" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="L9" s="61" t="s">
+      <c r="L9" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="M9" s="61"/>
-      <c r="N9" s="61"/>
-      <c r="O9" s="61" t="s">
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31" t="s">
         <v>421</v>
       </c>
-      <c r="P9" s="61"/>
-    </row>
-    <row r="10" spans="1:16" customHeight="1" ht="15">
-      <c r="A10" s="61" t="s">
+      <c r="P9" s="31"/>
+    </row>
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D10" s="61" t="s">
+      <c r="D10" s="31" t="s">
         <v>424</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="31">
         <v>2019</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="31">
         <v>8</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="31">
         <v>3000</v>
       </c>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61">
+      <c r="H10" s="31"/>
+      <c r="I10" s="31">
         <v>3000</v>
       </c>
-      <c r="J10" s="61" t="s">
+      <c r="J10" s="31" t="s">
         <v>425</v>
       </c>
-      <c r="K10" s="61" t="s">
+      <c r="K10" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L10" s="61"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-    </row>
-    <row r="11" spans="1:16" customHeight="1" ht="15">
-      <c r="A11" s="61" t="s">
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+    </row>
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D11" s="61" t="s">
+      <c r="D11" s="31" t="s">
         <v>426</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="31">
         <v>2019</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="31">
         <v>9</v>
       </c>
-      <c r="G11" s="61">
+      <c r="G11" s="31">
         <v>3000</v>
       </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61">
+      <c r="H11" s="31"/>
+      <c r="I11" s="31">
         <v>3000</v>
       </c>
-      <c r="J11" s="61" t="s">
+      <c r="J11" s="31" t="s">
         <v>427</v>
       </c>
-      <c r="K11" s="61" t="s">
+      <c r="K11" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="61"/>
-    </row>
-    <row r="12" spans="1:16" customHeight="1" ht="15">
-      <c r="A12" s="61" t="s">
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="D12" s="31" t="s">
         <v>428</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="31">
         <v>2019</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="31">
         <v>10</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G12" s="31">
         <v>3000</v>
       </c>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="61"/>
-      <c r="N12" s="61"/>
-      <c r="O12" s="61"/>
-      <c r="P12" s="61" t="s">
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:16" customHeight="1" ht="15">
-      <c r="A13" s="61" t="s">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="D13" s="61" t="s">
+      <c r="D13" s="31" t="s">
         <v>430</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="31">
         <v>2024</v>
       </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61">
+      <c r="F13" s="31"/>
+      <c r="G13" s="31">
         <v>800</v>
       </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61">
+      <c r="H13" s="31"/>
+      <c r="I13" s="31">
         <v>800</v>
       </c>
-      <c r="J13" s="61" t="s">
+      <c r="J13" s="31" t="s">
         <v>431</v>
       </c>
-      <c r="K13" s="61" t="s">
+      <c r="K13" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-    </row>
-    <row r="14" spans="1:16" customHeight="1" ht="15">
-      <c r="A14" s="61" t="s">
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+    </row>
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="31" t="s">
         <v>432</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="D14" s="61" t="s">
+      <c r="D14" s="31" t="s">
         <v>433</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="31">
         <v>2019</v>
       </c>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61">
+      <c r="F14" s="31"/>
+      <c r="G14" s="31">
         <v>80000</v>
       </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61">
+      <c r="H14" s="31"/>
+      <c r="I14" s="31">
         <v>80000</v>
       </c>
-      <c r="J14" s="61" t="s">
+      <c r="J14" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="K14" s="61" t="s">
+      <c r="K14" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L14" s="61" t="s">
+      <c r="L14" s="31" t="s">
         <v>435</v>
       </c>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61" t="s">
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31" t="s">
         <v>436</v>
       </c>
-      <c r="P14" s="61"/>
-    </row>
-    <row r="15" spans="1:16" customHeight="1" ht="15">
-      <c r="A15" s="61" t="s">
+      <c r="P14" s="31"/>
+    </row>
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
         <v>432</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D15" s="61" t="s">
+      <c r="D15" s="31" t="s">
         <v>415</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="31">
         <v>2019</v>
       </c>
-      <c r="F15" s="61">
+      <c r="F15" s="31">
         <v>3</v>
       </c>
-      <c r="G15" s="61">
+      <c r="G15" s="31">
         <v>3600</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61">
+      <c r="H15" s="31"/>
+      <c r="I15" s="31">
         <v>3600</v>
       </c>
-      <c r="J15" s="61" t="s">
+      <c r="J15" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="K15" s="61" t="s">
+      <c r="K15" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L15" s="61" t="s">
+      <c r="L15" s="31" t="s">
         <v>435</v>
       </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61" t="s">
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31" t="s">
         <v>436</v>
       </c>
-      <c r="P15" s="61"/>
-    </row>
-    <row r="16" spans="1:16" customHeight="1" ht="15">
-      <c r="A16" s="61" t="s">
+      <c r="P15" s="31"/>
+    </row>
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
         <v>432</v>
       </c>
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="31" t="s">
         <v>416</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="31">
         <v>2019</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="31">
         <v>4</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="31">
         <v>3600</v>
       </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61">
+      <c r="H16" s="31"/>
+      <c r="I16" s="31">
         <v>3600</v>
       </c>
-      <c r="J16" s="61" t="s">
+      <c r="J16" s="31" t="s">
         <v>437</v>
       </c>
-      <c r="K16" s="61" t="s">
+      <c r="K16" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L16" s="61" t="s">
+      <c r="L16" s="31" t="s">
         <v>438</v>
       </c>
-      <c r="M16" s="61"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="61" t="s">
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31" t="s">
         <v>439</v>
       </c>
-      <c r="P16" s="61"/>
-    </row>
-    <row r="17" spans="1:16" customHeight="1" ht="15">
-      <c r="A17" s="61" t="s">
+      <c r="P16" s="31"/>
+    </row>
+    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
         <v>432</v>
       </c>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="31" t="s">
         <v>418</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="31">
         <v>2019</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="31">
         <v>5</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="31">
         <v>3600</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61">
+      <c r="H17" s="31"/>
+      <c r="I17" s="31">
         <v>3600</v>
       </c>
-      <c r="J17" s="61" t="s">
+      <c r="J17" s="31" t="s">
         <v>437</v>
       </c>
-      <c r="K17" s="61" t="s">
+      <c r="K17" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L17" s="61" t="s">
+      <c r="L17" s="31" t="s">
         <v>438</v>
       </c>
-      <c r="M17" s="61"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="61" t="s">
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31" t="s">
         <v>439</v>
       </c>
-      <c r="P17" s="61"/>
-    </row>
-    <row r="18" spans="1:16" customHeight="1" ht="15">
-      <c r="A18" s="61" t="s">
+      <c r="P17" s="31"/>
+    </row>
+    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="31" t="s">
         <v>432</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="D18" s="31" t="s">
         <v>422</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="31">
         <v>2019</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="31">
         <v>6</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="31">
         <v>3600</v>
       </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61">
+      <c r="H18" s="31"/>
+      <c r="I18" s="31">
         <v>3600</v>
       </c>
-      <c r="J18" s="61" t="s">
+      <c r="J18" s="31" t="s">
         <v>437</v>
       </c>
-      <c r="K18" s="61" t="s">
+      <c r="K18" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L18" s="61" t="s">
+      <c r="L18" s="31" t="s">
         <v>438</v>
       </c>
-      <c r="M18" s="61"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="61" t="s">
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31" t="s">
         <v>439</v>
       </c>
-      <c r="P18" s="61"/>
-    </row>
-    <row r="19" spans="1:16" customHeight="1" ht="15">
-      <c r="A19" s="61" t="s">
+      <c r="P18" s="31"/>
+    </row>
+    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
         <v>440</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="D19" s="31" t="s">
         <v>441</v>
       </c>
-      <c r="E19" s="61">
+      <c r="E19" s="31">
         <v>2020</v>
       </c>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61">
+      <c r="F19" s="31"/>
+      <c r="G19" s="31">
         <v>45000</v>
       </c>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61">
+      <c r="H19" s="31"/>
+      <c r="I19" s="31">
         <v>45000</v>
       </c>
-      <c r="J19" s="61" t="s">
+      <c r="J19" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="K19" s="61" t="s">
+      <c r="K19" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="L19" s="61"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="61" t="s">
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="O19" s="61" t="s">
+      <c r="O19" s="31" t="s">
         <v>444</v>
       </c>
-      <c r="P19" s="61"/>
-    </row>
-    <row r="20" spans="1:16" customHeight="1" ht="15">
-      <c r="A20" s="61" t="s">
+      <c r="P19" s="31"/>
+    </row>
+    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="31" t="s">
         <v>440</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="31" t="s">
         <v>445</v>
       </c>
-      <c r="E20" s="61">
+      <c r="E20" s="31">
         <v>2020</v>
       </c>
-      <c r="F20" s="61">
+      <c r="F20" s="31">
         <v>6</v>
       </c>
-      <c r="G20" s="61">
+      <c r="G20" s="31">
         <v>1500</v>
       </c>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61">
+      <c r="H20" s="31"/>
+      <c r="I20" s="31">
         <v>1500</v>
       </c>
-      <c r="J20" s="61" t="s">
+      <c r="J20" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="K20" s="61" t="s">
+      <c r="K20" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61" t="s">
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="O20" s="61" t="s">
+      <c r="O20" s="31" t="s">
         <v>444</v>
       </c>
-      <c r="P20" s="61"/>
-    </row>
-    <row r="21" spans="1:16" customHeight="1" ht="15">
-      <c r="A21" s="61" t="s">
+      <c r="P20" s="31"/>
+    </row>
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
         <v>440</v>
       </c>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="E21" s="61">
+      <c r="E21" s="31">
         <v>2020</v>
       </c>
-      <c r="F21" s="61">
+      <c r="F21" s="31">
         <v>7</v>
       </c>
-      <c r="G21" s="61">
+      <c r="G21" s="31">
         <v>1500</v>
       </c>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61">
+      <c r="H21" s="31"/>
+      <c r="I21" s="31">
         <v>1500</v>
       </c>
-      <c r="J21" s="61" t="s">
+      <c r="J21" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="K21" s="61" t="s">
+      <c r="K21" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L21" s="61"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="61"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="61"/>
-    </row>
-    <row r="22" spans="1:16" customHeight="1" ht="15">
-      <c r="A22" s="61" t="s">
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+    </row>
+    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="D22" s="61" t="s">
+      <c r="D22" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="31">
         <v>2021</v>
       </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61">
+      <c r="F22" s="31"/>
+      <c r="G22" s="31">
         <v>40000</v>
       </c>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61">
+      <c r="H22" s="31"/>
+      <c r="I22" s="31">
         <v>40000</v>
       </c>
-      <c r="J22" s="61" t="s">
+      <c r="J22" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="K22" s="61" t="s">
+      <c r="K22" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L22" s="61" t="s">
+      <c r="L22" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="M22" s="61"/>
-      <c r="N22" s="61"/>
-      <c r="O22" s="61" t="s">
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31" t="s">
         <v>452</v>
       </c>
-      <c r="P22" s="61"/>
-    </row>
-    <row r="23" spans="1:16" customHeight="1" ht="15">
-      <c r="A23" s="61" t="s">
+      <c r="P22" s="31"/>
+    </row>
+    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D23" s="61" t="s">
+      <c r="D23" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="31">
         <v>2021</v>
       </c>
-      <c r="F23" s="61">
+      <c r="F23" s="31">
         <v>1</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="31">
         <v>1800</v>
       </c>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61">
+      <c r="H23" s="31"/>
+      <c r="I23" s="31">
         <v>1800</v>
       </c>
-      <c r="J23" s="61" t="s">
+      <c r="J23" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="K23" s="61" t="s">
+      <c r="K23" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L23" s="61" t="s">
+      <c r="L23" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="61" t="s">
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31" t="s">
         <v>452</v>
       </c>
-      <c r="P23" s="61"/>
-    </row>
-    <row r="24" spans="1:16" customHeight="1" ht="15">
-      <c r="A24" s="61" t="s">
+      <c r="P23" s="31"/>
+    </row>
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E24" s="31">
         <v>2021</v>
       </c>
-      <c r="F24" s="61">
+      <c r="F24" s="31">
         <v>2</v>
       </c>
-      <c r="G24" s="61">
+      <c r="G24" s="31">
         <v>1800</v>
       </c>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61">
+      <c r="H24" s="31"/>
+      <c r="I24" s="31">
         <v>1800</v>
       </c>
-      <c r="J24" s="61" t="s">
+      <c r="J24" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="K24" s="61" t="s">
+      <c r="K24" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L24" s="61" t="s">
+      <c r="L24" s="31" t="s">
         <v>456</v>
       </c>
-      <c r="M24" s="61"/>
-      <c r="N24" s="61"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="61"/>
-    </row>
-    <row r="25" spans="1:16" customHeight="1" ht="15">
-      <c r="A25" s="61" t="s">
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="31"/>
+    </row>
+    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="D25" s="31" t="s">
         <v>458</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="31">
         <v>2018</v>
       </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61">
+      <c r="F25" s="31"/>
+      <c r="G25" s="31">
         <v>160000</v>
       </c>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61">
+      <c r="H25" s="31"/>
+      <c r="I25" s="31">
         <v>160000</v>
       </c>
-      <c r="J25" s="61" t="s">
+      <c r="J25" s="31" t="s">
         <v>459</v>
       </c>
-      <c r="K25" s="61" t="s">
+      <c r="K25" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L25" s="61" t="s">
+      <c r="L25" s="31" t="s">
         <v>460</v>
       </c>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61"/>
-      <c r="O25" s="61" t="s">
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31" t="s">
         <v>461</v>
       </c>
-      <c r="P25" s="61"/>
-    </row>
-    <row r="26" spans="1:16" customHeight="1" ht="15">
-      <c r="A26" s="61" t="s">
+      <c r="P25" s="31"/>
+    </row>
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="31" t="s">
         <v>462</v>
       </c>
-      <c r="E26" s="61">
+      <c r="E26" s="31">
         <v>2018</v>
       </c>
-      <c r="F26" s="61">
+      <c r="F26" s="31">
         <v>9</v>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="31">
         <v>3600</v>
       </c>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61">
+      <c r="H26" s="31"/>
+      <c r="I26" s="31">
         <v>3600</v>
       </c>
-      <c r="J26" s="61" t="s">
+      <c r="J26" s="31" t="s">
         <v>459</v>
       </c>
-      <c r="K26" s="61" t="s">
+      <c r="K26" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="L26" s="61" t="s">
+      <c r="L26" s="31" t="s">
         <v>460</v>
       </c>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="61" t="s">
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31" t="s">
         <v>461</v>
       </c>
-      <c r="P26" s="61"/>
-    </row>
-    <row r="27" spans="1:16" customHeight="1" ht="15">
-      <c r="A27" s="61" t="s">
+      <c r="P26" s="31"/>
+    </row>
+    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="D27" s="31" t="s">
         <v>463</v>
       </c>
-      <c r="E27" s="61">
+      <c r="E27" s="31">
         <v>2018</v>
       </c>
-      <c r="F27" s="61">
+      <c r="F27" s="31">
         <v>10</v>
       </c>
-      <c r="G27" s="61">
+      <c r="G27" s="31">
         <v>3600</v>
       </c>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61">
+      <c r="H27" s="31"/>
+      <c r="I27" s="31">
         <v>3600</v>
       </c>
-      <c r="J27" s="61" t="s">
+      <c r="J27" s="31" t="s">
         <v>464</v>
       </c>
-      <c r="K27" s="61" t="s">
+      <c r="K27" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L27" s="61"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="61"/>
-      <c r="O27" s="61"/>
-      <c r="P27" s="61"/>
-    </row>
-    <row r="28" spans="1:16" customHeight="1" ht="15">
-      <c r="A28" s="61" t="s">
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+    </row>
+    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="E28" s="61">
+      <c r="E28" s="31">
         <v>2019</v>
       </c>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61">
+      <c r="F28" s="31"/>
+      <c r="G28" s="31">
         <v>700</v>
       </c>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61">
+      <c r="H28" s="31"/>
+      <c r="I28" s="31">
         <v>700</v>
       </c>
-      <c r="J28" s="61" t="s">
+      <c r="J28" s="31" t="s">
         <v>466</v>
       </c>
-      <c r="K28" s="61" t="s">
+      <c r="K28" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L28" s="61"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="61"/>
-      <c r="O28" s="61"/>
-      <c r="P28" s="61"/>
-    </row>
-    <row r="29" spans="1:16" customHeight="1" ht="15">
-      <c r="A29" s="61" t="s">
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+    </row>
+    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="D29" s="61" t="s">
+      <c r="D29" s="31" t="s">
         <v>467</v>
       </c>
-      <c r="E29" s="61">
+      <c r="E29" s="31">
         <v>2020</v>
       </c>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61">
+      <c r="F29" s="31"/>
+      <c r="G29" s="31">
         <v>700</v>
       </c>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61">
+      <c r="H29" s="31"/>
+      <c r="I29" s="31">
         <v>700</v>
       </c>
-      <c r="J29" s="61" t="s">
+      <c r="J29" s="31" t="s">
         <v>468</v>
       </c>
-      <c r="K29" s="61" t="s">
+      <c r="K29" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L29" s="61"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="61"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="61"/>
-    </row>
-    <row r="30" spans="1:16" customHeight="1" ht="15">
-      <c r="A30" s="61" t="s">
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+    </row>
+    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="31" t="s">
         <v>469</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="D30" s="31" t="s">
         <v>470</v>
       </c>
-      <c r="E30" s="61">
+      <c r="E30" s="31">
         <v>2022</v>
       </c>
-      <c r="F30" s="61">
+      <c r="F30" s="31">
         <v>1</v>
       </c>
-      <c r="G30" s="61">
+      <c r="G30" s="31">
         <v>750</v>
       </c>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61">
+      <c r="H30" s="31"/>
+      <c r="I30" s="31">
         <v>750</v>
       </c>
-      <c r="J30" s="61" t="s">
+      <c r="J30" s="31" t="s">
         <v>471</v>
       </c>
-      <c r="K30" s="61" t="s">
+      <c r="K30" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
-    </row>
-    <row r="31" spans="1:16" customHeight="1" ht="15">
-      <c r="A31" s="61" t="s">
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+    </row>
+    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="31" t="s">
         <v>469</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="D31" s="61" t="s">
+      <c r="D31" s="31" t="s">
         <v>472</v>
       </c>
-      <c r="E31" s="61">
+      <c r="E31" s="31">
         <v>2022</v>
       </c>
-      <c r="F31" s="61">
+      <c r="F31" s="31">
         <v>2</v>
       </c>
-      <c r="G31" s="61">
+      <c r="G31" s="31">
         <v>750</v>
       </c>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61" t="s">
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:16" customHeight="1" ht="15">
-      <c r="A32" s="60"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="60"/>
-      <c r="O32" s="60"/>
-      <c r="P32" s="60"/>
-    </row>
-    <row r="33" spans="1:16" customHeight="1" ht="30">
-      <c r="A33" s="30" t="s">
+    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+    </row>
+    <row r="33" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="43" t="s">
         <v>473</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A33:P33"/>
     <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.88671875" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11.6640625" customWidth="true" style="0"/>
-    <col min="4" max="4" width="11.6640625" customWidth="true" style="0"/>
-    <col min="5" max="5" width="20" customWidth="true" style="0"/>
-    <col min="6" max="6" width="10" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16" customWidth="true" style="0"/>
-    <col min="8" max="8" width="16" customWidth="true" style="0"/>
-    <col min="9" max="9" width="14" customWidth="true" style="0"/>
-    <col min="10" max="10" width="35" customWidth="true" style="0"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customHeight="1" ht="25.5">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>474</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-    </row>
-    <row r="2" spans="1:10" customHeight="1" ht="31.5">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+    </row>
+    <row r="2" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:10" customHeight="1" ht="42">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="16" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="16" t="s">
         <v>480</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>481</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="16" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="4" spans="1:10" customHeight="1" ht="15">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>238</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>2026</v>
       </c>
-      <c r="G4" s="62">
+      <c r="G4" s="42">
         <v>46023</v>
       </c>
-      <c r="H4" s="62">
+      <c r="H4" s="42">
         <v>46387</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" customHeight="1" ht="15">
-      <c r="A5" s="23" t="s">
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <v>15</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="18">
         <v>2023</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="18" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="6" spans="1:10" customHeight="1" ht="15">
-      <c r="A6" s="24"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-    </row>
-    <row r="7" spans="1:10" customHeight="1" ht="19.95">
-      <c r="A7" s="63" t="s">
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+    </row>
+    <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="43" t="s">
         <v>494</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>